--- a/results/cot_inference/mgsm/tiny-aya-global/summary_majority.xlsx
+++ b/results/cot_inference/mgsm/tiny-aya-global/summary_majority.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,28 +442,140 @@
           <t>accuracy</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>parse_failures</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Bengali</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>140</v>
+      </c>
+      <c r="D2" t="n">
+        <v>250</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>56.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Chinese</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>56.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>181</v>
+      </c>
+      <c r="D4" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>72.4%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Swahili</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>138</v>
+      </c>
+      <c r="D5" t="n">
+        <v>250</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>55.2%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>te</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>137</v>
+      </c>
+      <c r="D6" t="n">
+        <v>250</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>54.8%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/cot_inference/mgsm/tiny-aya-global/summary_majority.xlsx
+++ b/results/cot_inference/mgsm/tiny-aya-global/summary_majority.xlsx
@@ -460,14 +460,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D2" t="n">
         <v>250</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -486,14 +486,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="D3" t="n">
         <v>250</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -512,14 +512,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="D4" t="n">
         <v>250</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D5" t="n">
         <v>250</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -564,14 +564,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D6" t="n">
         <v>250</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
